--- a/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-11_Fornecedores_Ciclo_Vida.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-11_Fornecedores_Ciclo_Vida.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGA_Sistema-de-gestao-ambiental\Registos_SGA_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0924AE-C759-4F02-A2C7-193666DCCF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8177BE-9ADF-49A2-9A74-8DC678C48204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1200,7 +1200,7 @@
     <t>USA</t>
   </si>
   <si>
-    <t>HDPE, LDPE, MDPE</t>
+    <t>HDPE, HDPE-PCR, LDPE, MDPE</t>
   </si>
   <si>
     <t>Resina / matéria-prima</t>
